--- a/deliverables/User Stories-FILLED.xlsx
+++ b/deliverables/User Stories-FILLED.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/honesttape/Desktop/ALL/Currents /This Current/Codes/ITSC-3155-Group-Project-Group-19/deliverables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0C31BE-CDAA-F845-85D1-6D85DF9CC4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CE4D66-2BC6-FA42-854F-B536CEF41A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="128">
   <si>
     <t>ITSC-3155 Software Engineering</t>
   </si>
@@ -236,46 +236,46 @@
     <t>11.0</t>
   </si>
   <si>
-    <t>Payment processing (multiple methods)</t>
-  </si>
-  <si>
-    <t>pay using different payment methods</t>
-  </si>
-  <si>
-    <t>I can complete checkout with my preferred option</t>
-  </si>
-  <si>
-    <t>As a Customer I want to pay using different payment methods so that I can complete checkout with my preferred option</t>
+    <t>Payment processing (multiple methods, transaction status, failures)</t>
+  </si>
+  <si>
+    <t>pay using different payment methods and see whether my payment succeeded or failed</t>
+  </si>
+  <si>
+    <t>I can complete checkout and know if I need to retry</t>
+  </si>
+  <si>
+    <t>As a Customer I want to pay using different payment methods and see whether my payment succeeded or failed so that I can complete checkout and know if I need to retry</t>
   </si>
   <si>
     <t>12.0</t>
   </si>
   <si>
-    <t>Customer reviews &amp; ratings</t>
-  </si>
-  <si>
-    <t>leave a rating and review after an order</t>
-  </si>
-  <si>
-    <t>the restaurant can improve based on feedback</t>
-  </si>
-  <si>
-    <t>As a Customer I want to leave a rating and review after an order so that the restaurant can improve based on feedback</t>
+    <t>Customer reviews &amp; ratings (one review per order)</t>
+  </si>
+  <si>
+    <t>leave at most one rating and review for my completed order</t>
+  </si>
+  <si>
+    <t>the restaurant gets clear feedback without duplicate reviews</t>
+  </si>
+  <si>
+    <t>As a Customer I want to leave at most one rating and review for my completed order so that the restaurant gets clear feedback without duplicate reviews</t>
   </si>
   <si>
     <t>13.0</t>
   </si>
   <si>
-    <t>Promotions &amp; promo code generation</t>
-  </si>
-  <si>
-    <t>create promotions and promo codes</t>
-  </si>
-  <si>
-    <t>I can encourage repeat customers and increase sales</t>
-  </si>
-  <si>
-    <t>As a Restaurant manager I want to create promotions and promo codes so that I can encourage repeat customers and increase sales</t>
+    <t>Promotions: create codes; validate &amp; apply at checkout</t>
+  </si>
+  <si>
+    <t>create promotions and promo codes for customers</t>
+  </si>
+  <si>
+    <t>I can run marketing campaigns</t>
+  </si>
+  <si>
+    <t>As a Restaurant manager I want to create promotions and promo codes for customers so that I can run marketing campaigns</t>
   </si>
   <si>
     <t>14.0</t>
@@ -297,6 +297,123 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>enter a promo code during checkout</t>
+  </si>
+  <si>
+    <t>a valid discount is applied to my order</t>
+  </si>
+  <si>
+    <t>As a Customer I want to enter a promo code during checkout so that a valid discount is applied to my order</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>see a clear message when a promo code is invalid or expired</t>
+  </si>
+  <si>
+    <t>I can correct the code or continue without the discount</t>
+  </si>
+  <si>
+    <t>As a Customer I want to see a clear message when a promo code is invalid or expired so that I can correct the code or continue without the discount</t>
+  </si>
+  <si>
+    <t>17.0</t>
+  </si>
+  <si>
+    <t>retry payment after a failure</t>
+  </si>
+  <si>
+    <t>I can complete my order without starting over</t>
+  </si>
+  <si>
+    <t>As a Customer I want to retry payment after a failure so that I can complete my order without starting over</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>Order record: customer link, total price, status, tracking #, order type</t>
+  </si>
+  <si>
+    <t>see my order total before paying</t>
+  </si>
+  <si>
+    <t>I agree to the final amount before checkout completes</t>
+  </si>
+  <si>
+    <t>As a Customer I want to see my order total before paying so that I agree to the final amount before checkout completes</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>have my order linked to my name, phone, and address</t>
+  </si>
+  <si>
+    <t>staff can prepare and deliver my order correctly</t>
+  </si>
+  <si>
+    <t>As a Guest customer I want to have my order linked to my name, phone, and address so that staff can prepare and deliver my order correctly</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>Staff &amp; cook: update order status</t>
+  </si>
+  <si>
+    <t>update order status (e.g., received, preparing, ready)</t>
+  </si>
+  <si>
+    <t>customers see accurate progress on their order</t>
+  </si>
+  <si>
+    <t>As a Staff member I want to update order status (e.g., received, preparing, ready) so that customers see accurate progress on their order</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>update order status from the kitchen view</t>
+  </si>
+  <si>
+    <t>customers and front-of-house know when food is ready</t>
+  </si>
+  <si>
+    <t>As a Chef I want to update order status from the kitchen view so that customers and front-of-house know when food is ready</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>Documentation &amp; staff training materials</t>
+  </si>
+  <si>
+    <t>access onboarding and training materials for staff</t>
+  </si>
+  <si>
+    <t>new hires learn processes consistently</t>
+  </si>
+  <si>
+    <t>As a Restaurant owner I want to access onboarding and training materials for staff so that new hires learn processes consistently</t>
+  </si>
+  <si>
+    <t>23.0</t>
+  </si>
+  <si>
+    <t>filter analytics by date range or category</t>
+  </si>
+  <si>
+    <t>I can answer specific business questions quickly</t>
+  </si>
+  <si>
+    <t>As a Restaurant owner I want to filter analytics by date range or category so that I can answer specific business questions quickly</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -510,17 +627,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -551,12 +660,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -777,448 +898,685 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="3" width="31.5" customWidth="1"/>
-    <col min="4" max="4" width="34.1640625" customWidth="1"/>
-    <col min="5" max="5" width="33.6640625" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="1"/>
+    <col min="2" max="3" width="31.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1"/>
+    <col min="8" max="8" width="14.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="18"/>
+    </row>
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+    <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19">
-        <f>SUM(H4:H17)</f>
-        <v>75</v>
+      <c r="B18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="13" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="12">
+        <f>SUM(H4:H26)</f>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
